--- a/forms/trg/Formulir_TRG_cyberiot.xlsx
+++ b/forms/trg/Formulir_TRG_cyberiot.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Eng. Muhammad Niswar, S.T., M.IT.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1165,7 +1169,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1231,7 +1235,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1264,7 +1268,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1297,7 +1301,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
